--- a/artfynd/A 53019-2024 artfynd.xlsx
+++ b/artfynd/A 53019-2024 artfynd.xlsx
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121683021</v>
+        <v>121681118</v>
       </c>
       <c r="B6" t="n">
-        <v>57726</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,35 +1187,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577471</v>
+        <v>577524</v>
       </c>
       <c r="R6" t="n">
-        <v>6653486</v>
+        <v>6653467</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1254,22 +1254,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Indre Cepukaite</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121681118</v>
+        <v>121681117</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1352,10 +1352,10 @@
         <v>577524</v>
       </c>
       <c r="R7" t="n">
-        <v>6653467</v>
+        <v>6653475</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,47 +1425,47 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121681117</v>
+        <v>121683021</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>57726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577524</v>
+        <v>577471</v>
       </c>
       <c r="R8" t="n">
-        <v>6653475</v>
+        <v>6653486</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1504,22 +1504,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2024-04-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Indre Cepukaite</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 53019-2024 artfynd.xlsx
+++ b/artfynd/A 53019-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121681119</v>
+        <v>121681118</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577528</v>
+        <v>577524</v>
       </c>
       <c r="R2" t="n">
-        <v>6653454</v>
+        <v>6653467</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121681115</v>
+        <v>121681119</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577511</v>
+        <v>577528</v>
       </c>
       <c r="R3" t="n">
-        <v>6653447</v>
+        <v>6653454</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121681118</v>
+        <v>121681116</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577524</v>
+        <v>577531</v>
       </c>
       <c r="R4" t="n">
-        <v>6653467</v>
+        <v>6653461</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121680818</v>
+        <v>121681115</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,35 +1062,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577544</v>
+        <v>577511</v>
       </c>
       <c r="R5" t="n">
-        <v>6653481</v>
+        <v>6653447</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121681116</v>
+        <v>121680818</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,35 +1312,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577531</v>
+        <v>577544</v>
       </c>
       <c r="R7" t="n">
-        <v>6653461</v>
+        <v>6653481</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 53019-2024 artfynd.xlsx
+++ b/artfynd/A 53019-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121681118</v>
+        <v>121680818</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577524</v>
+        <v>577544</v>
       </c>
       <c r="R2" t="n">
-        <v>6653467</v>
+        <v>6653481</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121681116</v>
+        <v>121681115</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577531</v>
+        <v>577511</v>
       </c>
       <c r="R4" t="n">
-        <v>6653461</v>
+        <v>6653447</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121681115</v>
+        <v>121681116</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577511</v>
+        <v>577531</v>
       </c>
       <c r="R5" t="n">
-        <v>6653447</v>
+        <v>6653461</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121681117</v>
+        <v>121681118</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1227,10 +1227,10 @@
         <v>577524</v>
       </c>
       <c r="R6" t="n">
-        <v>6653475</v>
+        <v>6653467</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121680818</v>
+        <v>121681117</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,35 +1312,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577544</v>
+        <v>577524</v>
       </c>
       <c r="R7" t="n">
-        <v>6653481</v>
+        <v>6653475</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1545,6 +1545,135 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121864685</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98113</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ljusberget (knärot), Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>577523</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6653467</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>U-Sal-1099</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>X: (8) 5 pl, A: 634/808 (10) 3 pl, B: 651/815(5) 1 pl, C: 654/822 (5),4 pl, D: 648/836 (5) 10 pl proj. ledning Sala - Avesta Greenway AB</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Signe Vendike</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 53019-2024 artfynd.xlsx
+++ b/artfynd/A 53019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121680818</v>
+        <v>121681117</v>
       </c>
       <c r="B2" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577544</v>
+        <v>577524</v>
       </c>
       <c r="R2" t="n">
-        <v>6653481</v>
+        <v>6653475</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121681119</v>
+        <v>121681116</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577528</v>
+        <v>577531</v>
       </c>
       <c r="R3" t="n">
-        <v>6653454</v>
+        <v>6653461</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121681116</v>
+        <v>121681119</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577531</v>
+        <v>577528</v>
       </c>
       <c r="R5" t="n">
-        <v>6653461</v>
+        <v>6653454</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121681117</v>
+        <v>121680818</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,35 +1312,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577524</v>
+        <v>577544</v>
       </c>
       <c r="R7" t="n">
-        <v>6653475</v>
+        <v>6653481</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1598,7 +1598,7 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ljusberget (knärot), Vstm</t>
+          <t>Ljusberget SO (knärot), Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">

--- a/artfynd/A 53019-2024 artfynd.xlsx
+++ b/artfynd/A 53019-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121681117</v>
+        <v>121681119</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577524</v>
+        <v>577528</v>
       </c>
       <c r="R2" t="n">
-        <v>6653475</v>
+        <v>6653454</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121681116</v>
+        <v>121681115</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577531</v>
+        <v>577511</v>
       </c>
       <c r="R3" t="n">
-        <v>6653461</v>
+        <v>6653447</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121681115</v>
+        <v>121681118</v>
       </c>
       <c r="B4" t="n">
         <v>98113</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577511</v>
+        <v>577524</v>
       </c>
       <c r="R4" t="n">
-        <v>6653447</v>
+        <v>6653467</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121681119</v>
+        <v>121681116</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577528</v>
+        <v>577531</v>
       </c>
       <c r="R5" t="n">
-        <v>6653454</v>
+        <v>6653461</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121681118</v>
+        <v>121681117</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1227,10 +1227,10 @@
         <v>577524</v>
       </c>
       <c r="R6" t="n">
-        <v>6653467</v>
+        <v>6653475</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 53019-2024 artfynd.xlsx
+++ b/artfynd/A 53019-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121681115</v>
+        <v>121681117</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577511</v>
+        <v>577524</v>
       </c>
       <c r="R3" t="n">
-        <v>6653447</v>
+        <v>6653475</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121681118</v>
+        <v>121680818</v>
       </c>
       <c r="B4" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,35 +937,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577524</v>
+        <v>577544</v>
       </c>
       <c r="R4" t="n">
-        <v>6653467</v>
+        <v>6653481</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121681116</v>
+        <v>121681115</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577531</v>
+        <v>577511</v>
       </c>
       <c r="R5" t="n">
-        <v>6653461</v>
+        <v>6653447</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121681117</v>
+        <v>121681116</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577524</v>
+        <v>577531</v>
       </c>
       <c r="R6" t="n">
-        <v>6653475</v>
+        <v>6653461</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121680818</v>
+        <v>121681118</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,35 +1312,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577544</v>
+        <v>577524</v>
       </c>
       <c r="R7" t="n">
-        <v>6653481</v>
+        <v>6653467</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 53019-2024 artfynd.xlsx
+++ b/artfynd/A 53019-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121681119</v>
+        <v>121681115</v>
       </c>
       <c r="B2" t="n">
         <v>98113</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577528</v>
+        <v>577511</v>
       </c>
       <c r="R2" t="n">
-        <v>6653454</v>
+        <v>6653447</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121681117</v>
+        <v>121681116</v>
       </c>
       <c r="B3" t="n">
         <v>98113</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577524</v>
+        <v>577531</v>
       </c>
       <c r="R3" t="n">
-        <v>6653475</v>
+        <v>6653461</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121681115</v>
+        <v>121681117</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577511</v>
+        <v>577524</v>
       </c>
       <c r="R5" t="n">
-        <v>6653447</v>
+        <v>6653475</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121681116</v>
+        <v>121681118</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577531</v>
+        <v>577524</v>
       </c>
       <c r="R6" t="n">
-        <v>6653461</v>
+        <v>6653467</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121681118</v>
+        <v>121681119</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577524</v>
+        <v>577528</v>
       </c>
       <c r="R7" t="n">
-        <v>6653467</v>
+        <v>6653454</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 53019-2024 artfynd.xlsx
+++ b/artfynd/A 53019-2024 artfynd.xlsx
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121681118</v>
+        <v>121681119</v>
       </c>
       <c r="B6" t="n">
         <v>98113</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577524</v>
+        <v>577528</v>
       </c>
       <c r="R6" t="n">
-        <v>6653467</v>
+        <v>6653454</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121681119</v>
+        <v>121681118</v>
       </c>
       <c r="B7" t="n">
         <v>98113</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577528</v>
+        <v>577524</v>
       </c>
       <c r="R7" t="n">
-        <v>6653454</v>
+        <v>6653467</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 53019-2024 artfynd.xlsx
+++ b/artfynd/A 53019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121681115</v>
+        <v>121681118</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577511</v>
+        <v>577524</v>
       </c>
       <c r="R2" t="n">
-        <v>6653447</v>
+        <v>6653467</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121681116</v>
+        <v>121681117</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577531</v>
+        <v>577524</v>
       </c>
       <c r="R3" t="n">
-        <v>6653461</v>
+        <v>6653475</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121680818</v>
+        <v>121681115</v>
       </c>
       <c r="B4" t="n">
-        <v>90728</v>
+        <v>98131</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,35 +937,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577544</v>
+        <v>577511</v>
       </c>
       <c r="R4" t="n">
-        <v>6653481</v>
+        <v>6653447</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121681117</v>
+        <v>121680818</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>90742</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,35 +1062,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577524</v>
+        <v>577544</v>
       </c>
       <c r="R5" t="n">
-        <v>6653475</v>
+        <v>6653481</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,7 +1178,7 @@
         <v>121681119</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121681118</v>
+        <v>121681116</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577524</v>
+        <v>577531</v>
       </c>
       <c r="R7" t="n">
-        <v>6653467</v>
+        <v>6653461</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1428,7 +1428,7 @@
         <v>121683021</v>
       </c>
       <c r="B8" t="n">
-        <v>57726</v>
+        <v>57734</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>121864685</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 53019-2024 artfynd.xlsx
+++ b/artfynd/A 53019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121681118</v>
+        <v>121681115</v>
       </c>
       <c r="B2" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577524</v>
+        <v>577511</v>
       </c>
       <c r="R2" t="n">
-        <v>6653467</v>
+        <v>6653447</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121681117</v>
+        <v>121681118</v>
       </c>
       <c r="B3" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +852,10 @@
         <v>577524</v>
       </c>
       <c r="R3" t="n">
-        <v>6653475</v>
+        <v>6653467</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121681115</v>
+        <v>121681117</v>
       </c>
       <c r="B4" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577511</v>
+        <v>577524</v>
       </c>
       <c r="R4" t="n">
-        <v>6653447</v>
+        <v>6653475</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121680818</v>
+        <v>121681116</v>
       </c>
       <c r="B5" t="n">
-        <v>90742</v>
+        <v>98133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,35 +1062,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577544</v>
+        <v>577531</v>
       </c>
       <c r="R5" t="n">
-        <v>6653481</v>
+        <v>6653461</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121681119</v>
+        <v>121680818</v>
       </c>
       <c r="B6" t="n">
-        <v>98131</v>
+        <v>90744</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,25 +1187,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577528</v>
+        <v>577544</v>
       </c>
       <c r="R6" t="n">
-        <v>6653454</v>
+        <v>6653481</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121681116</v>
+        <v>121681119</v>
       </c>
       <c r="B7" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577531</v>
+        <v>577528</v>
       </c>
       <c r="R7" t="n">
-        <v>6653461</v>
+        <v>6653454</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1553,7 +1553,7 @@
         <v>121864685</v>
       </c>
       <c r="B9" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 53019-2024 artfynd.xlsx
+++ b/artfynd/A 53019-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121681115</v>
       </c>
       <c r="B2" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121681118</v>
+        <v>121681119</v>
       </c>
       <c r="B3" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577524</v>
+        <v>577528</v>
       </c>
       <c r="R3" t="n">
-        <v>6653467</v>
+        <v>6653454</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121681117</v>
+        <v>121680818</v>
       </c>
       <c r="B4" t="n">
-        <v>98133</v>
+        <v>90745</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,35 +937,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577524</v>
+        <v>577544</v>
       </c>
       <c r="R4" t="n">
-        <v>6653475</v>
+        <v>6653481</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121681116</v>
+        <v>121681117</v>
       </c>
       <c r="B5" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577531</v>
+        <v>577524</v>
       </c>
       <c r="R5" t="n">
-        <v>6653461</v>
+        <v>6653475</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121680818</v>
+        <v>121681116</v>
       </c>
       <c r="B6" t="n">
-        <v>90744</v>
+        <v>98140</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,35 +1187,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577544</v>
+        <v>577531</v>
       </c>
       <c r="R6" t="n">
-        <v>6653481</v>
+        <v>6653461</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121681119</v>
+        <v>121681118</v>
       </c>
       <c r="B7" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577528</v>
+        <v>577524</v>
       </c>
       <c r="R7" t="n">
-        <v>6653454</v>
+        <v>6653467</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1553,7 +1553,7 @@
         <v>121864685</v>
       </c>
       <c r="B9" t="n">
-        <v>98133</v>
+        <v>98140</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 53019-2024 artfynd.xlsx
+++ b/artfynd/A 53019-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121681115</v>
+        <v>121681118</v>
       </c>
       <c r="B2" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577511</v>
+        <v>577524</v>
       </c>
       <c r="R2" t="n">
-        <v>6653447</v>
+        <v>6653467</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121681119</v>
+        <v>121681117</v>
       </c>
       <c r="B3" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577528</v>
+        <v>577524</v>
       </c>
       <c r="R3" t="n">
-        <v>6653454</v>
+        <v>6653475</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121680818</v>
+        <v>121681119</v>
       </c>
       <c r="B4" t="n">
-        <v>90745</v>
+        <v>98149</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,25 +937,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577544</v>
+        <v>577528</v>
       </c>
       <c r="R4" t="n">
-        <v>6653481</v>
+        <v>6653454</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121681117</v>
+        <v>121680818</v>
       </c>
       <c r="B5" t="n">
-        <v>98140</v>
+        <v>90754</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,35 +1062,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577524</v>
+        <v>577544</v>
       </c>
       <c r="R5" t="n">
-        <v>6653475</v>
+        <v>6653481</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,7 +1178,7 @@
         <v>121681116</v>
       </c>
       <c r="B6" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1300,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121681118</v>
+        <v>121681115</v>
       </c>
       <c r="B7" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577524</v>
+        <v>577511</v>
       </c>
       <c r="R7" t="n">
-        <v>6653467</v>
+        <v>6653447</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1428,7 +1428,7 @@
         <v>121683021</v>
       </c>
       <c r="B8" t="n">
-        <v>57734</v>
+        <v>57738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>121864685</v>
       </c>
       <c r="B9" t="n">
-        <v>98140</v>
+        <v>98149</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 53019-2024 artfynd.xlsx
+++ b/artfynd/A 53019-2024 artfynd.xlsx
@@ -1553,7 +1553,7 @@
         <v>121864685</v>
       </c>
       <c r="B9" t="n">
-        <v>98149</v>
+        <v>98157</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 53019-2024 artfynd.xlsx
+++ b/artfynd/A 53019-2024 artfynd.xlsx
@@ -1553,7 +1553,7 @@
         <v>121864685</v>
       </c>
       <c r="B9" t="n">
-        <v>98157</v>
+        <v>98159</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 53019-2024 artfynd.xlsx
+++ b/artfynd/A 53019-2024 artfynd.xlsx
@@ -1553,7 +1553,7 @@
         <v>121864685</v>
       </c>
       <c r="B9" t="n">
-        <v>98159</v>
+        <v>98175</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
